--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548283</v>
+        <v>121548274</v>
       </c>
       <c r="B2" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,7 +709,11 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587786</v>
+        <v>587791</v>
       </c>
       <c r="R2" t="n">
-        <v>6385018</v>
+        <v>6385028</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +789,7 @@
         <v>121548226</v>
       </c>
       <c r="B3" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -893,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121548333</v>
+        <v>121548290</v>
       </c>
       <c r="B4" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587875</v>
+        <v>587787</v>
       </c>
       <c r="R4" t="n">
-        <v>6385053</v>
+        <v>6385007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121548237</v>
+        <v>121548283</v>
       </c>
       <c r="B5" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,24 +1042,20 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587789</v>
+        <v>587786</v>
       </c>
       <c r="R5" t="n">
-        <v>6385057</v>
+        <v>6385018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548323</v>
+        <v>121548300</v>
       </c>
       <c r="B6" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,14 +1159,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587855</v>
+        <v>587783</v>
       </c>
       <c r="R6" t="n">
-        <v>6385041</v>
+        <v>6385017</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548274</v>
+        <v>121548256</v>
       </c>
       <c r="B7" t="n">
-        <v>98099</v>
+        <v>90739</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,35 +1238,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1274,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587791</v>
+        <v>587818</v>
       </c>
       <c r="R7" t="n">
-        <v>6385028</v>
+        <v>6385047</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548316</v>
+        <v>121548305</v>
       </c>
       <c r="B8" t="n">
-        <v>98099</v>
+        <v>94876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,46 +1352,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587772</v>
+        <v>587774</v>
       </c>
       <c r="R8" t="n">
-        <v>6385021</v>
+        <v>6385016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548305</v>
+        <v>121548333</v>
       </c>
       <c r="B9" t="n">
-        <v>94871</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,42 +1459,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587774</v>
+        <v>587875</v>
       </c>
       <c r="R9" t="n">
-        <v>6385016</v>
+        <v>6385053</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548256</v>
+        <v>121548316</v>
       </c>
       <c r="B10" t="n">
-        <v>90734</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,49 +1570,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 59750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587818</v>
+        <v>587772</v>
       </c>
       <c r="R10" t="n">
-        <v>6385047</v>
+        <v>6385021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1672,7 @@
         <v>121548263</v>
       </c>
       <c r="B11" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548290</v>
+        <v>121548323</v>
       </c>
       <c r="B12" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587787</v>
+        <v>587855</v>
       </c>
       <c r="R12" t="n">
-        <v>6385007</v>
+        <v>6385041</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548300</v>
+        <v>121548237</v>
       </c>
       <c r="B13" t="n">
-        <v>98099</v>
+        <v>98104</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,14 +1935,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587783</v>
+        <v>587789</v>
       </c>
       <c r="R13" t="n">
-        <v>6385017</v>
+        <v>6385057</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548274</v>
+        <v>121548333</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587791</v>
+        <v>587875</v>
       </c>
       <c r="R2" t="n">
-        <v>6385028</v>
+        <v>6385053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121548226</v>
+        <v>121548237</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587785</v>
+        <v>587789</v>
       </c>
       <c r="R3" t="n">
-        <v>6385036</v>
+        <v>6385057</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121548290</v>
+        <v>121548305</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>94877</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,46 +909,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587787</v>
+        <v>587774</v>
       </c>
       <c r="R4" t="n">
-        <v>6385007</v>
+        <v>6385016</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121548283</v>
+        <v>121548316</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,20 +1038,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 59750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587786</v>
+        <v>587772</v>
       </c>
       <c r="R5" t="n">
-        <v>6385018</v>
+        <v>6385021</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548300</v>
+        <v>121548256</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>90740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,46 +1127,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587783</v>
+        <v>587818</v>
       </c>
       <c r="R6" t="n">
-        <v>6385017</v>
+        <v>6385047</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548256</v>
+        <v>121548300</v>
       </c>
       <c r="B7" t="n">
-        <v>90739</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,49 +1241,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587818</v>
+        <v>587783</v>
       </c>
       <c r="R7" t="n">
-        <v>6385047</v>
+        <v>6385017</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548305</v>
+        <v>121548283</v>
       </c>
       <c r="B8" t="n">
-        <v>94876</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,25 +1352,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,14 +1380,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587774</v>
+        <v>587786</v>
       </c>
       <c r="R8" t="n">
-        <v>6385016</v>
+        <v>6385018</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548333</v>
+        <v>121548226</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,14 +1491,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587875</v>
+        <v>587785</v>
       </c>
       <c r="R9" t="n">
-        <v>6385053</v>
+        <v>6385036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548316</v>
+        <v>121548263</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,11 +1602,11 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587772</v>
+        <v>587786</v>
       </c>
       <c r="R10" t="n">
         <v>6385021</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548263</v>
+        <v>121548323</v>
       </c>
       <c r="B11" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587786</v>
+        <v>587855</v>
       </c>
       <c r="R11" t="n">
-        <v>6385021</v>
+        <v>6385041</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548323</v>
+        <v>121548274</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587855</v>
+        <v>587791</v>
       </c>
       <c r="R12" t="n">
-        <v>6385041</v>
+        <v>6385028</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548237</v>
+        <v>121548290</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,14 +1935,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587789</v>
+        <v>587787</v>
       </c>
       <c r="R13" t="n">
-        <v>6385057</v>
+        <v>6385007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548333</v>
+        <v>121548263</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587875</v>
+        <v>587786</v>
       </c>
       <c r="R2" t="n">
-        <v>6385053</v>
+        <v>6385021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121548237</v>
+        <v>121548290</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587789</v>
+        <v>587787</v>
       </c>
       <c r="R3" t="n">
-        <v>6385057</v>
+        <v>6385007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121548305</v>
+        <v>121548300</v>
       </c>
       <c r="B4" t="n">
-        <v>94877</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,42 +909,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587774</v>
+        <v>587783</v>
       </c>
       <c r="R4" t="n">
-        <v>6385016</v>
+        <v>6385017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121548316</v>
+        <v>121548283</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1038,24 +1042,20 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587772</v>
+        <v>587786</v>
       </c>
       <c r="R5" t="n">
-        <v>6385021</v>
+        <v>6385018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548256</v>
+        <v>121548226</v>
       </c>
       <c r="B6" t="n">
-        <v>90740</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,49 +1127,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587818</v>
+        <v>587785</v>
       </c>
       <c r="R6" t="n">
-        <v>6385047</v>
+        <v>6385036</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548300</v>
+        <v>121548305</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>94877</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,46 +1238,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587783</v>
+        <v>587774</v>
       </c>
       <c r="R7" t="n">
-        <v>6385017</v>
+        <v>6385016</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548283</v>
+        <v>121548256</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>90740</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,31 +1345,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587786</v>
+        <v>587818</v>
       </c>
       <c r="R8" t="n">
-        <v>6385018</v>
+        <v>6385047</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548226</v>
+        <v>121548316</v>
       </c>
       <c r="B9" t="n">
         <v>98105</v>
@@ -1491,14 +1491,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 59750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587785</v>
+        <v>587772</v>
       </c>
       <c r="R9" t="n">
-        <v>6385036</v>
+        <v>6385021</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548263</v>
+        <v>121548323</v>
       </c>
       <c r="B10" t="n">
         <v>98105</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587786</v>
+        <v>587855</v>
       </c>
       <c r="R10" t="n">
-        <v>6385021</v>
+        <v>6385041</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548323</v>
+        <v>121548274</v>
       </c>
       <c r="B11" t="n">
         <v>98105</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587855</v>
+        <v>587791</v>
       </c>
       <c r="R11" t="n">
-        <v>6385041</v>
+        <v>6385028</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548274</v>
+        <v>121548333</v>
       </c>
       <c r="B12" t="n">
         <v>98105</v>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587791</v>
+        <v>587875</v>
       </c>
       <c r="R12" t="n">
-        <v>6385028</v>
+        <v>6385053</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548290</v>
+        <v>121548237</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1935,14 +1935,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587787</v>
+        <v>587789</v>
       </c>
       <c r="R13" t="n">
-        <v>6385007</v>
+        <v>6385057</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548263</v>
+        <v>121548283</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -709,11 +709,7 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -726,7 +722,7 @@
         <v>587786</v>
       </c>
       <c r="R2" t="n">
-        <v>6385021</v>
+        <v>6385018</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121548290</v>
+        <v>121548316</v>
       </c>
       <c r="B3" t="n">
         <v>98105</v>
@@ -830,14 +826,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 59750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587787</v>
+        <v>587772</v>
       </c>
       <c r="R3" t="n">
-        <v>6385007</v>
+        <v>6385021</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121548283</v>
+        <v>121548256</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>90740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,31 +1016,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587786</v>
+        <v>587818</v>
       </c>
       <c r="R5" t="n">
-        <v>6385018</v>
+        <v>6385047</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548226</v>
+        <v>121548333</v>
       </c>
       <c r="B6" t="n">
         <v>98105</v>
@@ -1159,14 +1162,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587785</v>
+        <v>587875</v>
       </c>
       <c r="R6" t="n">
-        <v>6385036</v>
+        <v>6385053</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548305</v>
+        <v>121548290</v>
       </c>
       <c r="B7" t="n">
-        <v>94877</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,42 +1241,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587774</v>
+        <v>587787</v>
       </c>
       <c r="R7" t="n">
-        <v>6385016</v>
+        <v>6385007</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548256</v>
+        <v>121548263</v>
       </c>
       <c r="B8" t="n">
-        <v>90740</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,38 +1352,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1384,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587818</v>
+        <v>587786</v>
       </c>
       <c r="R8" t="n">
-        <v>6385047</v>
+        <v>6385021</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548316</v>
+        <v>121548305</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>94877</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,46 +1463,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587772</v>
+        <v>587774</v>
       </c>
       <c r="R9" t="n">
-        <v>6385021</v>
+        <v>6385016</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548323</v>
+        <v>121548274</v>
       </c>
       <c r="B10" t="n">
         <v>98105</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587855</v>
+        <v>587791</v>
       </c>
       <c r="R10" t="n">
-        <v>6385041</v>
+        <v>6385028</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548274</v>
+        <v>121548226</v>
       </c>
       <c r="B11" t="n">
         <v>98105</v>
@@ -1713,14 +1713,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587791</v>
+        <v>587785</v>
       </c>
       <c r="R11" t="n">
-        <v>6385028</v>
+        <v>6385036</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548333</v>
+        <v>121548323</v>
       </c>
       <c r="B12" t="n">
         <v>98105</v>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587875</v>
+        <v>587855</v>
       </c>
       <c r="R12" t="n">
-        <v>6385053</v>
+        <v>6385041</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548283</v>
+        <v>121548290</v>
       </c>
       <c r="B2" t="n">
         <v>98105</v>
@@ -709,7 +709,11 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587786</v>
+        <v>587787</v>
       </c>
       <c r="R2" t="n">
-        <v>6385018</v>
+        <v>6385007</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121548316</v>
+        <v>121548305</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>94877</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,46 +798,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587772</v>
+        <v>587774</v>
       </c>
       <c r="R3" t="n">
-        <v>6385021</v>
+        <v>6385016</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121548300</v>
+        <v>121548333</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -937,14 +937,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587783</v>
+        <v>587875</v>
       </c>
       <c r="R4" t="n">
-        <v>6385017</v>
+        <v>6385053</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121548256</v>
+        <v>121548226</v>
       </c>
       <c r="B5" t="n">
-        <v>90740</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,49 +1016,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587818</v>
+        <v>587785</v>
       </c>
       <c r="R5" t="n">
-        <v>6385047</v>
+        <v>6385036</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548333</v>
+        <v>121548256</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>90740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,35 +1127,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587875</v>
+        <v>587818</v>
       </c>
       <c r="R6" t="n">
-        <v>6385053</v>
+        <v>6385047</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548290</v>
+        <v>121548283</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1263,11 +1263,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1277,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587787</v>
+        <v>587786</v>
       </c>
       <c r="R7" t="n">
-        <v>6385007</v>
+        <v>6385018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1336,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548263</v>
+        <v>121548274</v>
       </c>
       <c r="B8" t="n">
         <v>98105</v>
@@ -1388,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587786</v>
+        <v>587791</v>
       </c>
       <c r="R8" t="n">
-        <v>6385021</v>
+        <v>6385028</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548305</v>
+        <v>121548323</v>
       </c>
       <c r="B9" t="n">
-        <v>94877</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,42 +1459,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587774</v>
+        <v>587855</v>
       </c>
       <c r="R9" t="n">
-        <v>6385016</v>
+        <v>6385041</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548274</v>
+        <v>121548316</v>
       </c>
       <c r="B10" t="n">
         <v>98105</v>
@@ -1602,14 +1602,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 59750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587791</v>
+        <v>587772</v>
       </c>
       <c r="R10" t="n">
-        <v>6385028</v>
+        <v>6385021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548226</v>
+        <v>121548237</v>
       </c>
       <c r="B11" t="n">
         <v>98105</v>
@@ -1713,14 +1713,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587785</v>
+        <v>587789</v>
       </c>
       <c r="R11" t="n">
-        <v>6385036</v>
+        <v>6385057</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548323</v>
+        <v>121548300</v>
       </c>
       <c r="B12" t="n">
         <v>98105</v>
@@ -1824,14 +1824,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587855</v>
+        <v>587783</v>
       </c>
       <c r="R12" t="n">
-        <v>6385041</v>
+        <v>6385017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548237</v>
+        <v>121548263</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1935,14 +1935,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587789</v>
+        <v>587786</v>
       </c>
       <c r="R13" t="n">
-        <v>6385057</v>
+        <v>6385021</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548290</v>
+        <v>121548274</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587787</v>
+        <v>587791</v>
       </c>
       <c r="R2" t="n">
-        <v>6385007</v>
+        <v>6385028</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121548305</v>
+        <v>121548256</v>
       </c>
       <c r="B3" t="n">
-        <v>94877</v>
+        <v>90748</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,42 +798,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587774</v>
+        <v>587818</v>
       </c>
       <c r="R3" t="n">
-        <v>6385016</v>
+        <v>6385047</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +903,7 @@
         <v>121548333</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1004,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121548226</v>
+        <v>121548300</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587785</v>
+        <v>587783</v>
       </c>
       <c r="R5" t="n">
-        <v>6385036</v>
+        <v>6385017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548256</v>
+        <v>121548263</v>
       </c>
       <c r="B6" t="n">
-        <v>90740</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,38 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1166,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587818</v>
+        <v>587786</v>
       </c>
       <c r="R6" t="n">
-        <v>6385047</v>
+        <v>6385021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548283</v>
+        <v>121548323</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,7 +1267,11 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1273,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587786</v>
+        <v>587855</v>
       </c>
       <c r="R7" t="n">
-        <v>6385018</v>
+        <v>6385041</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548274</v>
+        <v>121548283</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,11 +1378,7 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1384,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587791</v>
+        <v>587786</v>
       </c>
       <c r="R8" t="n">
-        <v>6385028</v>
+        <v>6385018</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548323</v>
+        <v>121548226</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,14 +1495,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587855</v>
+        <v>587785</v>
       </c>
       <c r="R9" t="n">
-        <v>6385041</v>
+        <v>6385036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548316</v>
+        <v>121548290</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,14 +1606,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587772</v>
+        <v>587787</v>
       </c>
       <c r="R10" t="n">
-        <v>6385021</v>
+        <v>6385007</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548237</v>
+        <v>121548316</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,14 +1717,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 59750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587789</v>
+        <v>587772</v>
       </c>
       <c r="R11" t="n">
-        <v>6385057</v>
+        <v>6385021</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548300</v>
+        <v>121548305</v>
       </c>
       <c r="B12" t="n">
-        <v>98105</v>
+        <v>94885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,46 +1796,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587783</v>
+        <v>587774</v>
       </c>
       <c r="R12" t="n">
-        <v>6385017</v>
+        <v>6385016</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548263</v>
+        <v>121548237</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,14 +1935,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587786</v>
+        <v>587789</v>
       </c>
       <c r="R13" t="n">
-        <v>6385021</v>
+        <v>6385057</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548274</v>
+        <v>121548300</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587791</v>
+        <v>587783</v>
       </c>
       <c r="R2" t="n">
-        <v>6385028</v>
+        <v>6385017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121548316</v>
+        <v>121548290</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587772</v>
+        <v>587787</v>
       </c>
       <c r="R3" t="n">
-        <v>6385021</v>
+        <v>6385007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121548290</v>
+        <v>121548256</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,35 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587787</v>
+        <v>587818</v>
       </c>
       <c r="R4" t="n">
-        <v>6385007</v>
+        <v>6385047</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121548333</v>
+        <v>121548226</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1052,14 +1055,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587875</v>
+        <v>587785</v>
       </c>
       <c r="R5" t="n">
-        <v>6385053</v>
+        <v>6385036</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1337,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548256</v>
+        <v>121548274</v>
       </c>
       <c r="B8" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,38 +1352,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587818</v>
+        <v>587791</v>
       </c>
       <c r="R8" t="n">
-        <v>6385047</v>
+        <v>6385028</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548263</v>
+        <v>121548237</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1495,14 +1495,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587786</v>
+        <v>587789</v>
       </c>
       <c r="R9" t="n">
-        <v>6385021</v>
+        <v>6385057</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548305</v>
+        <v>121548263</v>
       </c>
       <c r="B10" t="n">
-        <v>94885</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,42 +1574,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587774</v>
+        <v>587786</v>
       </c>
       <c r="R10" t="n">
-        <v>6385016</v>
+        <v>6385021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548226</v>
+        <v>121548305</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>94885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,46 +1685,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587785</v>
+        <v>587774</v>
       </c>
       <c r="R11" t="n">
-        <v>6385036</v>
+        <v>6385016</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548237</v>
+        <v>121548316</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1824,14 +1824,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 59750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587789</v>
+        <v>587772</v>
       </c>
       <c r="R12" t="n">
-        <v>6385057</v>
+        <v>6385021</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,7 +1891,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548300</v>
+        <v>121548333</v>
       </c>
       <c r="B13" t="n">
         <v>98113</v>
@@ -1935,14 +1935,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587783</v>
+        <v>587875</v>
       </c>
       <c r="R13" t="n">
-        <v>6385017</v>
+        <v>6385053</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548300</v>
+        <v>121548256</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587783</v>
+        <v>587818</v>
       </c>
       <c r="R2" t="n">
-        <v>6385017</v>
+        <v>6385047</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121548290</v>
+        <v>121548274</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587787</v>
+        <v>587791</v>
       </c>
       <c r="R3" t="n">
-        <v>6385007</v>
+        <v>6385028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121548256</v>
+        <v>121548226</v>
       </c>
       <c r="B4" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,49 +912,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587818</v>
+        <v>587785</v>
       </c>
       <c r="R4" t="n">
-        <v>6385047</v>
+        <v>6385036</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121548226</v>
+        <v>121548290</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1055,14 +1055,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587785</v>
+        <v>587787</v>
       </c>
       <c r="R5" t="n">
-        <v>6385036</v>
+        <v>6385007</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548283</v>
+        <v>121548263</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1156,7 +1156,11 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1169,7 +1173,7 @@
         <v>587786</v>
       </c>
       <c r="R6" t="n">
-        <v>6385018</v>
+        <v>6385021</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548323</v>
+        <v>121548283</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1263,11 +1267,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587855</v>
+        <v>587786</v>
       </c>
       <c r="R7" t="n">
-        <v>6385041</v>
+        <v>6385018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548274</v>
+        <v>121548323</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587791</v>
+        <v>587855</v>
       </c>
       <c r="R8" t="n">
-        <v>6385028</v>
+        <v>6385041</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548237</v>
+        <v>121548333</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1495,14 +1495,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587789</v>
+        <v>587875</v>
       </c>
       <c r="R9" t="n">
-        <v>6385057</v>
+        <v>6385053</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548263</v>
+        <v>121548300</v>
       </c>
       <c r="B10" t="n">
         <v>98113</v>
@@ -1606,14 +1606,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587786</v>
+        <v>587783</v>
       </c>
       <c r="R10" t="n">
-        <v>6385021</v>
+        <v>6385017</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548305</v>
+        <v>121548237</v>
       </c>
       <c r="B11" t="n">
-        <v>94885</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,29 +1685,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1717,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587774</v>
+        <v>587789</v>
       </c>
       <c r="R11" t="n">
-        <v>6385016</v>
+        <v>6385057</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1891,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548333</v>
+        <v>121548305</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>94885</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,46 +1907,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587875</v>
+        <v>587774</v>
       </c>
       <c r="R13" t="n">
-        <v>6385053</v>
+        <v>6385016</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548256</v>
+        <v>121548305</v>
       </c>
       <c r="B2" t="n">
-        <v>90748</v>
+        <v>94885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587818</v>
+        <v>587774</v>
       </c>
       <c r="R2" t="n">
-        <v>6385047</v>
+        <v>6385016</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -900,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121548226</v>
+        <v>121548300</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -948,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587785</v>
+        <v>587783</v>
       </c>
       <c r="R4" t="n">
-        <v>6385036</v>
+        <v>6385017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1004,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121548290</v>
+        <v>121548323</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1059,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587787</v>
+        <v>587855</v>
       </c>
       <c r="R5" t="n">
-        <v>6385007</v>
+        <v>6385041</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548263</v>
+        <v>121548316</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1166,11 +1159,11 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 59750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587786</v>
+        <v>587772</v>
       </c>
       <c r="R6" t="n">
         <v>6385021</v>
@@ -1340,7 +1333,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548323</v>
+        <v>121548226</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1384,14 +1377,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587855</v>
+        <v>587785</v>
       </c>
       <c r="R8" t="n">
-        <v>6385041</v>
+        <v>6385036</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548333</v>
+        <v>121548263</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1499,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587875</v>
+        <v>587786</v>
       </c>
       <c r="R9" t="n">
-        <v>6385053</v>
+        <v>6385021</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548300</v>
+        <v>121548256</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,46 +1567,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587783</v>
+        <v>587818</v>
       </c>
       <c r="R10" t="n">
-        <v>6385017</v>
+        <v>6385047</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548237</v>
+        <v>121548333</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1717,14 +1713,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587789</v>
+        <v>587875</v>
       </c>
       <c r="R11" t="n">
-        <v>6385057</v>
+        <v>6385053</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548316</v>
+        <v>121548290</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1828,14 +1824,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587772</v>
+        <v>587787</v>
       </c>
       <c r="R12" t="n">
-        <v>6385021</v>
+        <v>6385007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548305</v>
+        <v>121548237</v>
       </c>
       <c r="B13" t="n">
-        <v>94885</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,29 +1903,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587774</v>
+        <v>587789</v>
       </c>
       <c r="R13" t="n">
-        <v>6385016</v>
+        <v>6385057</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548305</v>
+        <v>121548333</v>
       </c>
       <c r="B2" t="n">
-        <v>94885</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587774</v>
+        <v>587875</v>
       </c>
       <c r="R2" t="n">
-        <v>6385016</v>
+        <v>6385053</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121548274</v>
+        <v>121548316</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -826,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 59750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587791</v>
+        <v>587772</v>
       </c>
       <c r="R3" t="n">
-        <v>6385028</v>
+        <v>6385021</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121548300</v>
+        <v>121548256</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,46 +909,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587783</v>
+        <v>587818</v>
       </c>
       <c r="R4" t="n">
-        <v>6385017</v>
+        <v>6385047</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121548323</v>
+        <v>121548237</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1048,14 +1055,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587855</v>
+        <v>587789</v>
       </c>
       <c r="R5" t="n">
-        <v>6385041</v>
+        <v>6385057</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548316</v>
+        <v>121548263</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1159,11 +1166,11 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587772</v>
+        <v>587786</v>
       </c>
       <c r="R6" t="n">
         <v>6385021</v>
@@ -1226,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548283</v>
+        <v>121548226</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1260,20 +1267,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587786</v>
+        <v>587785</v>
       </c>
       <c r="R7" t="n">
-        <v>6385018</v>
+        <v>6385036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548226</v>
+        <v>121548274</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1377,14 +1388,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587785</v>
+        <v>587791</v>
       </c>
       <c r="R8" t="n">
-        <v>6385036</v>
+        <v>6385028</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548263</v>
+        <v>121548300</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1488,14 +1499,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587786</v>
+        <v>587783</v>
       </c>
       <c r="R9" t="n">
-        <v>6385021</v>
+        <v>6385017</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548256</v>
+        <v>121548305</v>
       </c>
       <c r="B10" t="n">
-        <v>90748</v>
+        <v>94885</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,49 +1578,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587818</v>
+        <v>587774</v>
       </c>
       <c r="R10" t="n">
-        <v>6385047</v>
+        <v>6385016</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548333</v>
+        <v>121548290</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1717,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587875</v>
+        <v>587787</v>
       </c>
       <c r="R11" t="n">
-        <v>6385053</v>
+        <v>6385007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,7 +1784,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548290</v>
+        <v>121548323</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1828,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587787</v>
+        <v>587855</v>
       </c>
       <c r="R12" t="n">
-        <v>6385007</v>
+        <v>6385041</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,7 +1895,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548237</v>
+        <v>121548283</v>
       </c>
       <c r="B13" t="n">
         <v>98113</v>
@@ -1925,24 +1929,20 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587789</v>
+        <v>587786</v>
       </c>
       <c r="R13" t="n">
-        <v>6385057</v>
+        <v>6385018</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548333</v>
+        <v>121548316</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 59750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587875</v>
+        <v>587772</v>
       </c>
       <c r="R2" t="n">
-        <v>6385053</v>
+        <v>6385021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121548316</v>
+        <v>121548300</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587772</v>
+        <v>587783</v>
       </c>
       <c r="R3" t="n">
-        <v>6385021</v>
+        <v>6385017</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121548256</v>
+        <v>121548263</v>
       </c>
       <c r="B4" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587818</v>
+        <v>587786</v>
       </c>
       <c r="R4" t="n">
-        <v>6385047</v>
+        <v>6385021</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1122,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548263</v>
+        <v>121548283</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1156,11 +1153,7 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1173,7 +1166,7 @@
         <v>587786</v>
       </c>
       <c r="R6" t="n">
-        <v>6385021</v>
+        <v>6385018</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1226,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548226</v>
+        <v>121548290</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1277,14 +1270,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587785</v>
+        <v>587787</v>
       </c>
       <c r="R7" t="n">
-        <v>6385036</v>
+        <v>6385007</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548274</v>
+        <v>121548333</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1392,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587791</v>
+        <v>587875</v>
       </c>
       <c r="R8" t="n">
-        <v>6385028</v>
+        <v>6385053</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1448,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548300</v>
+        <v>121548226</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1503,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587783</v>
+        <v>587785</v>
       </c>
       <c r="R9" t="n">
-        <v>6385017</v>
+        <v>6385036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548305</v>
+        <v>121548256</v>
       </c>
       <c r="B10" t="n">
-        <v>94885</v>
+        <v>90748</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,42 +1571,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587774</v>
+        <v>587818</v>
       </c>
       <c r="R10" t="n">
-        <v>6385016</v>
+        <v>6385047</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548290</v>
+        <v>121548323</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587787</v>
+        <v>587855</v>
       </c>
       <c r="R11" t="n">
-        <v>6385007</v>
+        <v>6385041</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548323</v>
+        <v>121548274</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587855</v>
+        <v>587791</v>
       </c>
       <c r="R12" t="n">
-        <v>6385041</v>
+        <v>6385028</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548283</v>
+        <v>121548305</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>94885</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,25 +1907,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1935,14 +1935,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587786</v>
+        <v>587774</v>
       </c>
       <c r="R13" t="n">
-        <v>6385018</v>
+        <v>6385016</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548316</v>
+        <v>121548283</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -709,24 +709,20 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587772</v>
+        <v>587786</v>
       </c>
       <c r="R2" t="n">
-        <v>6385021</v>
+        <v>6385018</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121548300</v>
+        <v>121548226</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -834,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587783</v>
+        <v>587785</v>
       </c>
       <c r="R3" t="n">
-        <v>6385017</v>
+        <v>6385036</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121548263</v>
+        <v>121548316</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -941,11 +937,11 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 59750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587786</v>
+        <v>587772</v>
       </c>
       <c r="R4" t="n">
         <v>6385021</v>
@@ -1119,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548283</v>
+        <v>121548256</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,31 +1127,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1163,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587786</v>
+        <v>587818</v>
       </c>
       <c r="R6" t="n">
-        <v>6385018</v>
+        <v>6385047</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548290</v>
+        <v>121548300</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1270,14 +1273,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587787</v>
+        <v>587783</v>
       </c>
       <c r="R7" t="n">
-        <v>6385007</v>
+        <v>6385017</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548333</v>
+        <v>121548323</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1385,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587875</v>
+        <v>587855</v>
       </c>
       <c r="R8" t="n">
-        <v>6385053</v>
+        <v>6385041</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548226</v>
+        <v>121548305</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>94885</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,46 +1463,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587785</v>
+        <v>587774</v>
       </c>
       <c r="R9" t="n">
-        <v>6385036</v>
+        <v>6385016</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548256</v>
+        <v>121548263</v>
       </c>
       <c r="B10" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,38 +1570,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1610,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587818</v>
+        <v>587786</v>
       </c>
       <c r="R10" t="n">
-        <v>6385047</v>
+        <v>6385021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548323</v>
+        <v>121548274</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1721,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587855</v>
+        <v>587791</v>
       </c>
       <c r="R11" t="n">
-        <v>6385041</v>
+        <v>6385028</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121548274</v>
+        <v>121548290</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1832,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587791</v>
+        <v>587787</v>
       </c>
       <c r="R12" t="n">
-        <v>6385028</v>
+        <v>6385007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548305</v>
+        <v>121548333</v>
       </c>
       <c r="B13" t="n">
-        <v>94885</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,42 +1903,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587774</v>
+        <v>587875</v>
       </c>
       <c r="R13" t="n">
-        <v>6385016</v>
+        <v>6385053</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 58750-2024 artfynd.xlsx
+++ b/artfynd/A 58750-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121548283</v>
+        <v>121548305</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +710,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587786</v>
+        <v>587774</v>
       </c>
       <c r="R2" t="n">
-        <v>6385018</v>
+        <v>6385016</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,58 +777,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121548226</v>
+        <v>121548256</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 58750, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587785</v>
+        <v>587818</v>
       </c>
       <c r="R3" t="n">
-        <v>6385036</v>
+        <v>6385047</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121548316</v>
+        <v>121548187</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,14 +925,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 59750, S Stämshult, Sm</t>
+          <t>A 58750n S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587772</v>
+        <v>587647</v>
       </c>
       <c r="R4" t="n">
-        <v>6385021</v>
+        <v>6384901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,15 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121548237</v>
+        <v>121548202</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,14 +1031,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587789</v>
+        <v>587657</v>
       </c>
       <c r="R5" t="n">
-        <v>6385057</v>
+        <v>6384901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,50 +1098,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121548256</v>
+        <v>121548214</v>
       </c>
       <c r="B6" t="n">
-        <v>90748</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1166,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587818</v>
+        <v>587661</v>
       </c>
       <c r="R6" t="n">
-        <v>6385047</v>
+        <v>6384907</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,15 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121548300</v>
+        <v>121548226</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587783</v>
+        <v>587785</v>
       </c>
       <c r="R7" t="n">
-        <v>6385017</v>
+        <v>6385036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,15 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548323</v>
+        <v>121548237</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,14 +1349,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750. S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587855</v>
+        <v>587789</v>
       </c>
       <c r="R8" t="n">
-        <v>6385041</v>
+        <v>6385057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,54 +1416,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121548305</v>
+        <v>121548263</v>
       </c>
       <c r="B9" t="n">
-        <v>94885</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 58750. S Stämshult, Sm</t>
+          <t>A 58750, S Stämshult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587774</v>
+        <v>587786</v>
       </c>
       <c r="R9" t="n">
-        <v>6385016</v>
+        <v>6385021</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,15 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121548263</v>
+        <v>121548274</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587786</v>
+        <v>587791</v>
       </c>
       <c r="R10" t="n">
-        <v>6385021</v>
+        <v>6385028</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,15 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121548274</v>
+        <v>121548283</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,11 +1657,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1717,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587791</v>
+        <v>587786</v>
       </c>
       <c r="R11" t="n">
-        <v>6385028</v>
+        <v>6385018</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,12 +1733,7 @@
         <v>121548290</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,15 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121548333</v>
+        <v>121548300</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,14 +1875,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 58750, S Stämshult, Sm</t>
+          <t>A 58750, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587875</v>
+        <v>587783</v>
       </c>
       <c r="R13" t="n">
-        <v>6385053</v>
+        <v>6385017</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,6 +1939,324 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121548316</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 59750, S Stämshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>587772</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6385021</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121548323</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 58750, S Stämshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>587855</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6385041</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121548333</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 58750, S Stämshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>587875</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6385053</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
